--- a/reports/member_funnel/downloads/member_funnel_1d_target_cart_abandon.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_target_cart_abandon.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,22 +519,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>wooyes</t>
+          <t>kk_4755812472</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>01093487391</t>
+          <t>01022651918</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -575,12 +575,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>kk_4755812472</t>
+          <t>antonio34</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>01022651918</t>
+          <t>01090296238</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -603,22 +603,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>antonio34</t>
+          <t>kk_4814460268</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>01090296238</t>
+          <t>01064733325</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_CH_MESSAGE_0325_PRODUCT1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -641,7 +641,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -659,22 +659,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kk_4814460268</t>
+          <t>kk_3587558636</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>01064733325</t>
+          <t>01054029614</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_PRODUCT1</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -687,22 +687,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kk_3016906903</t>
+          <t>josolha</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>01050555122</t>
+          <t>01052056266</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -715,22 +715,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>josolha</t>
+          <t>kk_3016906903</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>01052056266</t>
+          <t>01050555122</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -743,22 +743,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kk_3587558636</t>
+          <t>somsea</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>01054029614</t>
+          <t>01028811570</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>EDM_0209_LIGHTBAG</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -771,12 +771,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>greom73</t>
+          <t>mezzo304</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>01086372526</t>
+          <t>01032400300</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -799,22 +799,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>somsea</t>
+          <t>kk_3817523531</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>01028811570</t>
+          <t>01090061449</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EDM_0209_LIGHTBAG</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -827,22 +827,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>goril04624</t>
+          <t>kk_4293591148</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>01047651746</t>
+          <t>01086489252</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -855,12 +855,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kk_4829516327</t>
+          <t>kk_3754413887</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>01098876431</t>
+          <t>01063758898</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -883,22 +883,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>mezzo304</t>
+          <t>kk_3226525569</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>01032400300</t>
+          <t>01066771348</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -911,22 +911,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>kk_3817523531</t>
+          <t>ilrove</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>01090061449</t>
+          <t>01095892077</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>EDM_0314</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -939,22 +939,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>kk_3226525569</t>
+          <t>kingca00769</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>01066771348</t>
+          <t>01093510084</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -967,22 +967,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>kk_4293591148</t>
+          <t>kk_2921230742</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>01086489252</t>
+          <t>01047459117</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -995,22 +995,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>kk_3754413887</t>
+          <t>kk_4279317974</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>01063758898</t>
+          <t>01086395686</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1023,12 +1023,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>zollee77</t>
+          <t>oh8811</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>01064740702</t>
+          <t>01094437389</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -1079,12 +1079,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>oh8811</t>
+          <t>julee4487</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>01094437389</t>
+          <t>01035614487</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -1107,12 +1107,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>kk_4279317974</t>
+          <t>phs76825</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>01086395686</t>
+          <t>01091406949</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -1135,22 +1135,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>kingca00769</t>
+          <t>kk_4312822884</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>01093510084</t>
+          <t>01021980502</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -1163,22 +1163,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>kk_2921230742</t>
+          <t>ehdtjd3321</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>01047459117</t>
+          <t>01083285317</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
@@ -1191,12 +1191,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ilrove</t>
+          <t>kk_2945164322</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>01095892077</t>
+          <t>01031165607</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>EDM_0314</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -1219,22 +1219,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>kk_4822475920</t>
+          <t>kk_4497254131</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>01073932582</t>
+          <t>01049355494</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -1247,22 +1247,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ehdtjd3321</t>
+          <t>kk_3922513902</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>01083285317</t>
+          <t>01063131027</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -1303,22 +1303,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>kk_3672780564</t>
+          <t>kk_4834119648</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>01089459294</t>
+          <t>01032402442</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -1331,12 +1331,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>kk_4839289649</t>
+          <t>salwoo</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>01041713878</t>
+          <t>01035285763</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1359,12 +1359,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>kk_4834119648</t>
+          <t>jamisu</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>01032402442</t>
+          <t>01047544340</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -1387,22 +1387,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>kk_4312822884</t>
+          <t>kk_4831600231</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>01021980502</t>
+          <t>01046650519</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -1415,12 +1415,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>kk_4497254131</t>
+          <t>kk_4234864746</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>01049355494</t>
+          <t>01062301880</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -1443,12 +1443,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>julee4487</t>
+          <t>kk_4422614826</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>01035614487</t>
+          <t>01067869772</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -1471,12 +1471,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>s09635</t>
+          <t>iamgabi0</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>01090472784</t>
+          <t>01028422324</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -1499,12 +1499,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>phs76825</t>
+          <t>kjchan69</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>01091406949</t>
+          <t>01063792010</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -1527,12 +1527,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>salwoo</t>
+          <t>kk_2824348249</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>01035285763</t>
+          <t>01025435357</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -1555,22 +1555,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>kk_3922513902</t>
+          <t>luxurykim11</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>01063131027</t>
+          <t>01093252716</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -1583,22 +1583,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>kk_2945164322</t>
+          <t>kk_3101303470</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>01031165607</t>
+          <t>01065980201</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -1611,12 +1611,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>jamisu</t>
+          <t>kk_2805794827</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>01047544340</t>
+          <t>01098906270</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -1639,22 +1639,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>kjchan69</t>
+          <t>kk_4839277282</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>01063792010</t>
+          <t>01045519906</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -1667,22 +1667,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>kk_4422614826</t>
+          <t>ymvianne</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>01067869772</t>
+          <t>01091979009</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -1695,22 +1695,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>kk_2824348249</t>
+          <t>kk_4838986411</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>01025435357</t>
+          <t>01093175607</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -1723,22 +1723,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>luxurykim11</t>
+          <t>queen704</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>01093252716</t>
+          <t>01030909790</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -1751,22 +1751,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>kk_4831600231</t>
+          <t>kk_4817163496</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>01046650519</t>
+          <t>01035959174</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -1779,12 +1779,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>kk_4326567662</t>
+          <t>kk_4741668082</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>01046049921</t>
+          <t>01035796093</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>120212705670680427</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -1807,22 +1807,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>kk_4836613952</t>
+          <t>kk_4841152170</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>01041344927</t>
+          <t>01050200309</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -1835,12 +1835,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>kk_4234864746</t>
+          <t>kk_4840949436</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>01062301880</t>
+          <t>01064495993</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -1863,22 +1863,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>iamgabi0</t>
+          <t>kk_4840338408</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>01028422324</t>
+          <t>01054621177</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -1891,22 +1891,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>kk_4836691459</t>
+          <t>kk_4815312274</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>01072445075</t>
+          <t>01050357610</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -1919,22 +1919,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ymvianne</t>
+          <t>kk_4841155697</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>01091979009</t>
+          <t>01041762160</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -1947,22 +1947,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>kk_3101303470</t>
+          <t>kk_4841564061</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>01065980201</t>
+          <t>01088968580</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -1975,22 +1975,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>kk_4741668082</t>
+          <t>kk_3483369286</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>01035796093</t>
+          <t>01088087188</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -2003,22 +2003,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>kk_4839277282</t>
+          <t>cloud84</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>01045519906</t>
+          <t>01094808884</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>EDM_0411</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -2031,22 +2031,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>kk_4838986411</t>
+          <t>kk_4303227124</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>01093175607</t>
+          <t>01037747441</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -2059,22 +2059,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>kk_4817163496</t>
+          <t>kk_3721509519</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>01035959174</t>
+          <t>01097118472</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -2087,12 +2087,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>kk_4840292707</t>
+          <t>kk_4840930255</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>01085257253</t>
+          <t>01092600071</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>120212705670680427</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -2115,22 +2115,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>kk_4815312274</t>
+          <t>kk_4841470777</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>01050357610</t>
+          <t>01067860344</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -2143,22 +2143,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kk_4485686054</t>
+          <t>akilris</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>01030613096</t>
+          <t>01076225525</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -2171,22 +2171,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>kk_2805794827</t>
+          <t>kk_4568748102</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>01098906270</t>
+          <t>01054073523</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -2199,22 +2199,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>hw00185</t>
+          <t>kk_4841572668</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>01032596566</t>
+          <t>01024164342</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -2227,12 +2227,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>kk_4840338408</t>
+          <t>jyseoul</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>01054621177</t>
+          <t>01054813799</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2255,194 +2255,26 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>queen704</t>
+          <t>kk_4840872605</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>01030909790</t>
+          <t>01063782216</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
-        <is>
-          <t>CART_REMINDER</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>kk_4303227124</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>01037747441</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>CART_REMINDER</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>kk_4439122782</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>01028252500</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>CART_REMINDER</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>cloud84</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>01094808884</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>CART_REMINDER</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>kk_3483369286</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>01088087188</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>CART_REMINDER</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>kk_3721509519</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>01097118472</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>CART_REMINDER</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>akilris</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>01076225525</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>etc</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
         </is>

--- a/reports/member_funnel/downloads/member_funnel_1d_target_cart_abandon.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_1d_target_cart_abandon.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,22 +519,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>kk_4755812472</t>
+          <t>kk_4270962450</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>01022651918</t>
+          <t>01065174170</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -547,22 +547,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>kk_4270962450</t>
+          <t>kk_4755812472</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>01065174170</t>
+          <t>01022651918</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -659,12 +659,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kk_3587558636</t>
+          <t>josolha</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>01054029614</t>
+          <t>01052056266</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -687,12 +687,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>josolha</t>
+          <t>kk_3587558636</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>01052056266</t>
+          <t>01054029614</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -827,12 +827,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kk_4293591148</t>
+          <t>kk_3754413887</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>01086489252</t>
+          <t>01063758898</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -855,22 +855,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kk_3754413887</t>
+          <t>ilrove</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>01063758898</t>
+          <t>01095892077</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>EDM_0314</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -883,22 +883,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>kk_3226525569</t>
+          <t>kk_4293591148</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>01066771348</t>
+          <t>01086489252</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -911,22 +911,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ilrove</t>
+          <t>kk_3226525569</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>01095892077</t>
+          <t>01066771348</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EDM_0314</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -939,12 +939,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>kingca00769</t>
+          <t>kk_4279317974</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>01093510084</t>
+          <t>01086395686</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -967,22 +967,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>kk_2921230742</t>
+          <t>oh8811</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>01047459117</t>
+          <t>01094437389</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -995,12 +995,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>kk_4279317974</t>
+          <t>kingca00769</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>01086395686</t>
+          <t>01093510084</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1023,22 +1023,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>oh8811</t>
+          <t>kk_2921230742</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>01094437389</t>
+          <t>01047459117</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -1079,12 +1079,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>julee4487</t>
+          <t>phs76825</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>01035614487</t>
+          <t>01091406949</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1107,12 +1107,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>phs76825</t>
+          <t>julee4487</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>01091406949</t>
+          <t>01035614487</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1135,22 +1135,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>kk_4312822884</t>
+          <t>kk_4834119648</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>01021980502</t>
+          <t>01032402442</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -1163,12 +1163,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ehdtjd3321</t>
+          <t>salwoo</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>01083285317</t>
+          <t>01035285763</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1191,12 +1191,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>kk_2945164322</t>
+          <t>kk_3922513902</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>01031165607</t>
+          <t>01063131027</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -1219,22 +1219,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>kk_4497254131</t>
+          <t>kk_4312822884</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>01049355494</t>
+          <t>01021980502</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -1247,22 +1247,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>kk_3922513902</t>
+          <t>ehdtjd3321</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>01063131027</t>
+          <t>01083285317</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -1303,12 +1303,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>kk_4834119648</t>
+          <t>kk_4497254131</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>01032402442</t>
+          <t>01049355494</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -1331,22 +1331,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>salwoo</t>
+          <t>kk_2945164322</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>01035285763</t>
+          <t>01031165607</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -1359,12 +1359,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>jamisu</t>
+          <t>kk_2824348249</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>01047544340</t>
+          <t>01025435357</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -1387,22 +1387,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>kk_4831600231</t>
+          <t>kk_4422614826</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>01046650519</t>
+          <t>01067869772</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -1415,12 +1415,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>kk_4234864746</t>
+          <t>kjchan69</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>01062301880</t>
+          <t>01063792010</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -1443,12 +1443,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>kk_4422614826</t>
+          <t>kk_4234864746</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>01067869772</t>
+          <t>01062301880</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -1471,12 +1471,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>iamgabi0</t>
+          <t>kk_4831600231</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>01028422324</t>
+          <t>01046650519</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1499,12 +1499,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>kjchan69</t>
+          <t>jamisu</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>01063792010</t>
+          <t>01047544340</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -1527,22 +1527,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>kk_2824348249</t>
+          <t>iamgabi0</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>01025435357</t>
+          <t>01028422324</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -1583,22 +1583,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>kk_3101303470</t>
+          <t>queen704</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>01065980201</t>
+          <t>01030909790</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -1611,22 +1611,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>kk_2805794827</t>
+          <t>kk_4839277282</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>01098906270</t>
+          <t>01045519906</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -1639,22 +1639,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>kk_4839277282</t>
+          <t>kk_4841155697</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>01045519906</t>
+          <t>01041762160</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -1667,22 +1667,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ymvianne</t>
+          <t>kk_4815312274</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>01091979009</t>
+          <t>01050357610</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -1695,12 +1695,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>kk_4838986411</t>
+          <t>kk_4841152170</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>01093175607</t>
+          <t>01050200309</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -1723,22 +1723,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>queen704</t>
+          <t>kk_2805794827</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>01030909790</t>
+          <t>01098906270</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -1751,22 +1751,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>kk_4817163496</t>
+          <t>kk_3101303470</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>01035959174</t>
+          <t>01065980201</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -1779,12 +1779,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>kk_4741668082</t>
+          <t>kk_4840338408</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>01035796093</t>
+          <t>01054621177</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -1807,12 +1807,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>kk_4841152170</t>
+          <t>kk_4838986411</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>01050200309</t>
+          <t>01093175607</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -1835,22 +1835,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>kk_4840949436</t>
+          <t>kk_4741668082</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>01064495993</t>
+          <t>01035796093</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>120212705670680427</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -1863,22 +1863,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>kk_4840338408</t>
+          <t>kk_4817163496</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>01054621177</t>
+          <t>01035959174</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -1891,22 +1891,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>kk_4815312274</t>
+          <t>kk_4841564061</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>01050357610</t>
+          <t>01088968580</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -1919,22 +1919,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>kk_4841155697</t>
+          <t>ymvianne</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>01041762160</t>
+          <t>01091979009</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -1947,17 +1947,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>kk_4841564061</t>
+          <t>kk_4840949436</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>01088968580</t>
+          <t>01064495993</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1975,22 +1975,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>kk_3483369286</t>
+          <t>akilris</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>01088087188</t>
+          <t>01076225525</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -2031,12 +2031,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>kk_4303227124</t>
+          <t>kk_4840930255</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>01037747441</t>
+          <t>01092600071</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>120212705670680427</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -2059,12 +2059,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>kk_3721509519</t>
+          <t>kk_4841572668</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>01097118472</t>
+          <t>01024164342</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -2087,12 +2087,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>kk_4840930255</t>
+          <t>kk_3721509519</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>01092600071</t>
+          <t>01097118472</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>120212705670680427</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -2143,22 +2143,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>akilris</t>
+          <t>kk_4568748102</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>01076225525</t>
+          <t>01054073523</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -2171,22 +2171,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>kk_4568748102</t>
+          <t>kk_4840872605</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>01054073523</t>
+          <t>01063782216</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -2199,12 +2199,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>kk_4841572668</t>
+          <t>kk_4303227124</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>01024164342</t>
+          <t>01037747441</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -2227,54 +2227,26 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>jyseoul</t>
+          <t>kk_3483369286</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>01054813799</t>
+          <t>01088087188</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
-        <is>
-          <t>CART_REMINDER</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>kk_4840872605</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>01063782216</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Organic Traffic</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>(organic)</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr">
         <is>
           <t>CART_REMINDER</t>
         </is>
